--- a/debug_tools/query/admin/knowledge_data.xlsx
+++ b/debug_tools/query/admin/knowledge_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="24750" windowHeight="11480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>embed_content</t>
   </si>
@@ -49,6 +49,14 @@
   </si>
   <si>
     <t>充值</t>
+  </si>
+  <si>
+    <t>如何使用微信充值？</t>
+  </si>
+  <si>
+    <t>1.打开手机微信 
+2.扫描二维码
+3.输入密码确认支付</t>
   </si>
 </sst>
 </file>
@@ -982,11 +990,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="2"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="20.75" customWidth="1"/>
-    <col min="2" max="2" width="19.75" customWidth="1"/>
+    <col min="1" max="1" width="20.7545454545455" customWidth="1"/>
+    <col min="2" max="2" width="19.7545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1000,7 +1008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="40.5" spans="1:3">
+    <row r="2" ht="42" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1008,6 +1016,17 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="42" spans="1:3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1022,7 +1041,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1034,7 +1053,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
